--- a/data/gravel/Scott Scale Gravel 2025.xlsx
+++ b/data/gravel/Scott Scale Gravel 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76ADEBB1-E693-1A42-933A-F06998F2DA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77EB18A-E5D4-9747-9F8D-9ACF225639D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24020" yWindow="-20580" windowWidth="27600" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11860" yWindow="1000" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="124">
   <si>
     <t>brand</t>
   </si>
@@ -399,6 +399,12 @@
   </si>
   <si>
     <t>a8:f34</t>
+  </si>
+  <si>
+    <t>internal</t>
+  </si>
+  <si>
+    <t>semi-integrated</t>
   </si>
 </sst>
 </file>
@@ -1980,10 +1986,16 @@
       <c r="A60" t="s">
         <v>65</v>
       </c>
+      <c r="B60" s="1" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>66</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Scott Scale Gravel 2025.xlsx
+++ b/data/gravel/Scott Scale Gravel 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77EB18A-E5D4-9747-9F8D-9ACF225639D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF9D8BD-F360-F64A-897A-1A69E15B48F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11860" yWindow="1000" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -405,6 +405,9 @@
   </si>
   <si>
     <t>semi-integrated</t>
+  </si>
+  <si>
+    <t>https://asset.scott-sports.com/fit-in/2000x2000/423/4235417969_2136239_2.png?signature=09aa8c31159001ac69fb26b639e3ce5c39bf9d1406aebbbeacf0e72317ea5af7</t>
   </si>
 </sst>
 </file>
@@ -821,6 +824,11 @@
         <v>106</v>
       </c>
     </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>124</v>
+      </c>
+    </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Scott Scale Gravel 2025.xlsx
+++ b/data/gravel/Scott Scale Gravel 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF9D8BD-F360-F64A-897A-1A69E15B48F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90266B8-294A-2340-A456-65C7E4D6A870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -290,9 +290,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
@@ -353,9 +350,6 @@
     <t>Scale Gravel</t>
   </si>
   <si>
-    <t>https://www.scott-sports.com/gb/en/products/bike-bikes-gravel-scale-gravel?gad_source=1&amp;gad_campaignid=22435656715&amp;gbraid=0AAAAACkUuTZewhVHZLBPS-oiJj0sVmEkF&amp;gclid=Cj0KCQjwnovFBhDnARIsAO4V7mAwcoCsaQsiz8o_vxYhYBKnzkmTuXcX_zm05n3GhKVnkw01yepU9-kaAqcbEALw_wcB</t>
-  </si>
-  <si>
     <t>flat bar</t>
   </si>
   <si>
@@ -408,6 +402,12 @@
   </si>
   <si>
     <t>https://asset.scott-sports.com/fit-in/2000x2000/423/4235417969_2136239_2.png?signature=09aa8c31159001ac69fb26b639e3ce5c39bf9d1406aebbbeacf0e72317ea5af7</t>
+  </si>
+  <si>
+    <t>https://www.scott-sports.com/us/en/products/bike-bikes-gravel-scale-gravel?gad_source=1&amp;gad_campaignid=22435656715&amp;gbraid=0AAAAACkUuTZewhVHZLBPS-oiJj0sVmEkF&amp;gclid=Cj0KCQjwnovFBhDnARIsAO4V7mAwcoCsaQsiz8o_vxYhYBKnzkmTuXcX_zm05n3GhKVnkw01yepU9-kaAqcbEALw_wcB</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -797,7 +797,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
@@ -821,12 +821,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
@@ -834,7 +834,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -842,32 +842,32 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>87</v>
-      </c>
       <c r="F8" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J8" s="6"/>
       <c r="L8" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M8" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="N8" s="6" t="s">
-        <v>87</v>
-      </c>
       <c r="O8" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
@@ -899,7 +899,7 @@
         <v>67.900000000000006</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>9</v>
@@ -945,7 +945,7 @@
         <v>120</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>11</v>
@@ -988,7 +988,7 @@
         <v>656.5</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>13</v>
@@ -1031,7 +1031,7 @@
         <v>835.1</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>15</v>
@@ -1074,7 +1074,7 @@
         <v>62</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>17</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>18</v>
@@ -1117,7 +1117,7 @@
         <v>313</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>18</v>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G15" s="7"/>
       <c r="J15" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>20</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>21</v>
@@ -1196,7 +1196,7 @@
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="J16" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>21</v>
@@ -1231,7 +1231,7 @@
         <v>530</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>23</v>
@@ -1274,7 +1274,7 @@
         <v>75.3</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>25</v>
@@ -1319,7 +1319,7 @@
         <v>425</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>27</v>
@@ -1362,7 +1362,7 @@
         <v>491.2</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>29</v>
@@ -1405,7 +1405,7 @@
         <v>628.1</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>31</v>
@@ -1433,7 +1433,7 @@
         <v>35</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C22" s="4">
         <v>50</v>
@@ -1448,10 +1448,10 @@
         <v>80</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="L22" s="4">
         <v>50</v>
@@ -1473,10 +1473,10 @@
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C23" s="4">
         <v>105</v>
@@ -1494,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="L23" s="4">
         <v>105</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C24" s="4">
         <v>506</v>
@@ -1534,10 +1534,10 @@
         <v>506</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L24" s="4">
         <v>506</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C25" s="4">
         <v>160</v>
@@ -1577,10 +1577,10 @@
         <v>300</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="L25" s="4">
         <v>160</v>
@@ -1605,7 +1605,7 @@
         <v>33</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C26" s="4">
         <v>170</v>
@@ -1620,10 +1620,10 @@
         <v>175</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L26" s="4">
         <v>170</v>
@@ -1837,7 +1837,7 @@
         <v>80</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -1845,7 +1845,7 @@
         <v>81</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -1935,7 +1935,7 @@
         <v>56</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -1995,7 +1995,7 @@
         <v>65</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -2003,7 +2003,7 @@
         <v>66</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
@@ -2070,7 +2070,7 @@
         <v>77</v>
       </c>
       <c r="B72">
-        <v>8999</v>
+        <v>2899</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
@@ -2083,7 +2083,7 @@
         <v>79</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Scott Scale Gravel 2025.xlsx
+++ b/data/gravel/Scott Scale Gravel 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90266B8-294A-2340-A456-65C7E4D6A870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D16BF8-19C5-2142-847E-3D10915E72C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="127">
   <si>
     <t>brand</t>
   </si>
@@ -408,6 +408,12 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Givisiez, Switzerland</t>
   </si>
 </sst>
 </file>
@@ -777,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y74"/>
+  <dimension ref="A1:Y75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -2086,6 +2092,14 @@
         <v>124</v>
       </c>
     </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>125</v>
+      </c>
+      <c r="B75" t="s">
+        <v>126</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Scott Scale Gravel 2025.xlsx
+++ b/data/gravel/Scott Scale Gravel 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D16BF8-19C5-2142-847E-3D10915E72C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0841E37C-3968-1147-8F58-E0754DC5E95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1764,20 +1764,16 @@
         <v>40</v>
       </c>
       <c r="C33">
-        <f>C35</f>
         <v>160</v>
       </c>
       <c r="D33">
-        <f>AVERAGE(D35,C36)</f>
-        <v>169.5</v>
+        <v>169</v>
       </c>
       <c r="E33">
-        <f t="shared" ref="E33:F33" si="1">AVERAGE(E35,D36)</f>
-        <v>179.5</v>
+        <v>179</v>
       </c>
       <c r="F33">
-        <f t="shared" si="1"/>
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1788,34 +1784,16 @@
         <v>41</v>
       </c>
       <c r="C34">
-        <f>D33</f>
-        <v>169.5</v>
+        <v>170</v>
       </c>
       <c r="D34">
-        <f t="shared" ref="D34:F34" si="2">E33</f>
-        <v>179.5</v>
+        <v>180</v>
       </c>
       <c r="E34">
-        <f t="shared" si="2"/>
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C35">
-        <v>160</v>
-      </c>
-      <c r="D35">
-        <v>169</v>
-      </c>
-      <c r="E35">
-        <v>179</v>
-      </c>
-      <c r="F35">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1824,18 +1802,6 @@
       </c>
       <c r="B36" t="s">
         <v>43</v>
-      </c>
-      <c r="C36">
-        <v>170</v>
-      </c>
-      <c r="D36">
-        <v>180</v>
-      </c>
-      <c r="E36">
-        <v>188</v>
-      </c>
-      <c r="F36">
-        <v>196</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">

--- a/data/gravel/Scott Scale Gravel 2025.xlsx
+++ b/data/gravel/Scott Scale Gravel 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0841E37C-3968-1147-8F58-E0754DC5E95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69DF22C4-BD1A-1E4F-85DD-1CEB38E7C276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="133">
   <si>
     <t>brand</t>
   </si>
@@ -414,6 +414,24 @@
   </si>
   <si>
     <t>Givisiez, Switzerland</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -783,7 +801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y75"/>
+  <dimension ref="A1:Y81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -1904,165 +1922,195 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>56</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>58</v>
-      </c>
-      <c r="B53">
-        <v>31.6</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>59</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>62</v>
-      </c>
-      <c r="B57">
-        <v>180</v>
+        <v>56</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>63</v>
-      </c>
-      <c r="B58">
-        <v>160</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>31.6</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>66</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>70</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>66</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>77</v>
-      </c>
-      <c r="B72">
-        <v>2899</v>
+        <v>71</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>79</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>2899</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>79</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>125</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>126</v>
       </c>
     </row>

--- a/data/gravel/Scott Scale Gravel 2025.xlsx
+++ b/data/gravel/Scott Scale Gravel 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69DF22C4-BD1A-1E4F-85DD-1CEB38E7C276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1AFF04-4D63-9F47-9BE5-8E15B396EF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10420" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="135">
   <si>
     <t>brand</t>
   </si>
@@ -392,9 +392,6 @@
     <t>press fit</t>
   </si>
   <si>
-    <t>a8:f34</t>
-  </si>
-  <si>
     <t>internal</t>
   </si>
   <si>
@@ -432,6 +429,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:f36</t>
   </si>
 </sst>
 </file>
@@ -801,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y81"/>
+  <dimension ref="A1:Y83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -845,12 +851,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
@@ -858,7 +864,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -1689,10 +1695,22 @@
       <c r="T27" s="4"/>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="3"/>
+      <c r="A28" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="4">
+        <v>0</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4">
+        <v>0</v>
+      </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="4"/>
@@ -1706,412 +1724,458 @@
       <c r="T28" s="4"/>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>36</v>
-      </c>
+      <c r="A29" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="4">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="4"/>
+      <c r="T29" s="4"/>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30">
-        <v>29</v>
-      </c>
-      <c r="D30">
-        <v>29</v>
-      </c>
-      <c r="E30">
-        <v>29</v>
-      </c>
-      <c r="F30">
-        <v>29</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="4"/>
+      <c r="T30" s="4"/>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32">
+        <v>29</v>
+      </c>
+      <c r="D32">
+        <v>29</v>
+      </c>
+      <c r="E32">
+        <v>29</v>
+      </c>
+      <c r="F32">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>38</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B33" t="s">
         <v>38</v>
       </c>
-      <c r="C31">
+      <c r="C33">
         <f>2.35*25.4</f>
         <v>59.69</v>
       </c>
-      <c r="D31">
-        <f t="shared" ref="D31:F31" si="0">2.35*25.4</f>
+      <c r="D33">
+        <f t="shared" ref="D33:F33" si="0">2.35*25.4</f>
         <v>59.69</v>
       </c>
-      <c r="E31">
+      <c r="E33">
         <f t="shared" si="0"/>
         <v>59.69</v>
       </c>
-      <c r="F31">
+      <c r="F33">
         <f t="shared" si="0"/>
         <v>59.69</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32">
-        <v>45</v>
-      </c>
-      <c r="D32">
-        <v>45</v>
-      </c>
-      <c r="E32">
-        <v>45</v>
-      </c>
-      <c r="F32">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33">
-        <v>160</v>
-      </c>
-      <c r="D33">
-        <v>169</v>
-      </c>
-      <c r="E33">
-        <v>179</v>
-      </c>
-      <c r="F33">
-        <v>184</v>
-      </c>
-    </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C34">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="D34">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="E34">
-        <v>188</v>
+        <v>45</v>
       </c>
       <c r="F34">
-        <v>196</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35">
+        <v>160</v>
+      </c>
+      <c r="D35">
+        <v>169</v>
+      </c>
+      <c r="E35">
+        <v>179</v>
+      </c>
+      <c r="F35">
+        <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>80</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>106</v>
+        <v>41</v>
+      </c>
+      <c r="C36">
+        <v>170</v>
+      </c>
+      <c r="D36">
+        <v>180</v>
+      </c>
+      <c r="E36">
+        <v>188</v>
+      </c>
+      <c r="F36">
+        <v>196</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>81</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>105</v>
+        <v>42</v>
+      </c>
+      <c r="B38" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>82</v>
-      </c>
-      <c r="B39" t="s">
-        <v>83</v>
+        <v>80</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" t="s">
-        <v>45</v>
+        <v>81</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>46</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
+      </c>
+      <c r="B41" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>44</v>
+      </c>
+      <c r="B42" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>48</v>
       </c>
-      <c r="B43">
+      <c r="B45">
         <f>2.35*25.4</f>
         <v>59.69</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>50</v>
-      </c>
-      <c r="B45">
-        <v>120</v>
-      </c>
-    </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="B47">
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>54</v>
-      </c>
-      <c r="B49">
-        <v>148</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>55</v>
-      </c>
-      <c r="B50">
-        <v>110</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>127</v>
+        <v>54</v>
+      </c>
+      <c r="B51">
+        <v>148</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>128</v>
+        <v>55</v>
+      </c>
+      <c r="B52">
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>56</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>57</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>58</v>
-      </c>
-      <c r="B59">
-        <v>31.6</v>
+        <v>56</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>59</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="B61">
+        <v>31.6</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>61</v>
+        <v>59</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>62</v>
-      </c>
-      <c r="B63">
-        <v>180</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>63</v>
-      </c>
-      <c r="B64">
-        <v>160</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+      <c r="B65">
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>65</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>121</v>
+        <v>63</v>
+      </c>
+      <c r="B66">
+        <v>160</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>66</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>120</v>
+        <v>64</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>68</v>
+        <v>66</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>69</v>
-      </c>
-      <c r="B70">
-        <v>2</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>70</v>
-      </c>
-      <c r="B71">
-        <v>1</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>71</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>84</v>
+        <v>69</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>72</v>
+        <v>70</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>73</v>
+        <v>71</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>77</v>
-      </c>
-      <c r="B78">
-        <v>2899</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>79</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>124</v>
+        <v>77</v>
+      </c>
+      <c r="B80">
+        <v>2899</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>79</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>124</v>
+      </c>
+      <c r="B83" t="s">
         <v>125</v>
-      </c>
-      <c r="B81" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>
